--- a/data/raw/sales/Week 27/Fossil/Seller Sales (SP-API).xlsx
+++ b/data/raw/sales/Week 27/Fossil/Seller Sales (SP-API).xlsx
@@ -1355,10 +1355,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G16" t="n">
-        <v>35069.49</v>
+        <v>29224.58</v>
       </c>
       <c r="H16" t="n">
         <v>13782</v>
